--- a/src/width_txt/Максимальные_значения_адаптивного_фильтра_АЦП_№3.xlsx
+++ b/src/width_txt/Максимальные_значения_адаптивного_фильтра_АЦП_№3.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="80" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="112" uniqueCount="8">
   <si>
     <t>Row</t>
   </si>
@@ -106,10 +106,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>6.489877763978739e+24</v>
+        <v>31282278042015</v>
       </c>
       <c r="C2" s="0">
-        <v>2.7389017023598816e+24</v>
+        <v>31282278039967</v>
       </c>
     </row>
     <row r="3">
@@ -117,10 +117,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="0">
-        <v>6.489877763978739e+24</v>
+        <v>2467873138185</v>
       </c>
       <c r="C3" s="0">
-        <v>1.3637515908004762e+24</v>
+        <v>9486484273126</v>
       </c>
     </row>
     <row r="4">
@@ -128,10 +128,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="0">
-        <v>2.7389017023598816e+24</v>
+        <v>31282278042015</v>
       </c>
       <c r="C4" s="0">
-        <v>5.5530664917623922e+24</v>
+        <v>9486484275174</v>
       </c>
     </row>
     <row r="5">
@@ -139,10 +139,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="0">
-        <v>5.5530664917623922e+24</v>
+        <v>2467873138185</v>
       </c>
       <c r="C5" s="0">
-        <v>60718374005238</v>
+        <v>276869254</v>
       </c>
     </row>
     <row r="6">
@@ -150,7 +150,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>5.5530664917623922e+24</v>
+        <v>9486484273126</v>
       </c>
       <c r="C6" s="0">
         <v>0</v>

--- a/src/width_txt/Максимальные_значения_адаптивного_фильтра_АЦП_№3.xlsx
+++ b/src/width_txt/Максимальные_значения_адаптивного_фильтра_АЦП_№3.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="112" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="210" uniqueCount="30">
   <si>
     <t>Row</t>
   </si>
@@ -33,10 +33,76 @@
     <t>5</t>
   </si>
   <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
     <t>Multipliers_adaptive</t>
   </si>
   <si>
-    <t>Sum_adaptive</t>
+    <t>Sum1_adaptive</t>
+  </si>
+  <si>
+    <t>Sum2_adaptive</t>
+  </si>
+  <si>
+    <t>Sum3_adaptive</t>
   </si>
 </sst>
 </file>
@@ -82,12 +148,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="true"/>
     <col min="2" max="2" width="19.5703125" customWidth="true"/>
-    <col min="3" max="3" width="15.85546875" customWidth="true"/>
+    <col min="3" max="3" width="14.7109375" customWidth="true"/>
+    <col min="4" max="4" width="14.7109375" customWidth="true"/>
+    <col min="5" max="5" width="14.7109375" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -95,10 +163,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>7</v>
+        <v>27</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1" s="0" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="2">
@@ -106,10 +180,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>31282278042015</v>
+        <v>3344893431</v>
       </c>
       <c r="C2" s="0">
-        <v>31282278039967</v>
+        <v>2066059023</v>
+      </c>
+      <c r="D2" s="0">
+        <v>2229261062</v>
+      </c>
+      <c r="E2" s="0">
+        <v>35340893</v>
       </c>
     </row>
     <row r="3">
@@ -117,10 +197,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="0">
-        <v>2467873138185</v>
+        <v>2844963288</v>
       </c>
       <c r="C3" s="0">
-        <v>9486484273126</v>
+        <v>2164435128</v>
+      </c>
+      <c r="D3" s="0">
+        <v>2107287535</v>
+      </c>
+      <c r="E3" s="0">
+        <v>27034777</v>
       </c>
     </row>
     <row r="4">
@@ -128,10 +214,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="0">
-        <v>31282278042015</v>
+        <v>2065003546</v>
       </c>
       <c r="C4" s="0">
-        <v>9486484275174</v>
+        <v>1916727202</v>
+      </c>
+      <c r="D4" s="0">
+        <v>2084066545</v>
+      </c>
+      <c r="E4" s="0">
+        <v>27313239</v>
       </c>
     </row>
     <row r="5">
@@ -139,10 +231,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="0">
-        <v>2467873138185</v>
+        <v>2049684826</v>
       </c>
       <c r="C5" s="0">
-        <v>276869254</v>
+        <v>2373864724</v>
+      </c>
+      <c r="D5" s="0">
+        <v>2892238098</v>
+      </c>
+      <c r="E5" s="0">
+        <v>31933693</v>
       </c>
     </row>
     <row r="6">
@@ -150,9 +248,355 @@
         <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>9486484273126</v>
+        <v>2157119488</v>
       </c>
       <c r="C6" s="0">
+        <v>1574629241</v>
+      </c>
+      <c r="D6" s="0">
+        <v>3404704306</v>
+      </c>
+      <c r="E6" s="0">
+        <v>33835067</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="0">
+        <v>1278834408</v>
+      </c>
+      <c r="C7" s="0">
+        <v>2349374751</v>
+      </c>
+      <c r="D7" s="0">
+        <v>0</v>
+      </c>
+      <c r="E7" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="0">
+        <v>1003679697</v>
+      </c>
+      <c r="C8" s="0">
+        <v>1571479617</v>
+      </c>
+      <c r="D8" s="0">
+        <v>0</v>
+      </c>
+      <c r="E8" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="0">
+        <v>1178733066</v>
+      </c>
+      <c r="C9" s="0">
+        <v>2095162035</v>
+      </c>
+      <c r="D9" s="0">
+        <v>0</v>
+      </c>
+      <c r="E9" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="0">
+        <v>1240516608</v>
+      </c>
+      <c r="C10" s="0">
+        <v>1725973047</v>
+      </c>
+      <c r="D10" s="0">
+        <v>0</v>
+      </c>
+      <c r="E10" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="0">
+        <v>1178127345</v>
+      </c>
+      <c r="C11" s="0">
+        <v>2920854919</v>
+      </c>
+      <c r="D11" s="0">
+        <v>0</v>
+      </c>
+      <c r="E11" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="0">
+        <v>1587891282</v>
+      </c>
+      <c r="C12" s="0">
+        <v>0</v>
+      </c>
+      <c r="D12" s="0">
+        <v>0</v>
+      </c>
+      <c r="E12" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="0">
+        <v>1213250429</v>
+      </c>
+      <c r="C13" s="0">
+        <v>0</v>
+      </c>
+      <c r="D13" s="0">
+        <v>0</v>
+      </c>
+      <c r="E13" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="0">
+        <v>1498807259</v>
+      </c>
+      <c r="C14" s="0">
+        <v>0</v>
+      </c>
+      <c r="D14" s="0">
+        <v>0</v>
+      </c>
+      <c r="E14" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="0">
+        <v>1213250429</v>
+      </c>
+      <c r="C15" s="0">
+        <v>0</v>
+      </c>
+      <c r="D15" s="0">
+        <v>0</v>
+      </c>
+      <c r="E15" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" s="0">
+        <v>1589212323</v>
+      </c>
+      <c r="C16" s="0">
+        <v>0</v>
+      </c>
+      <c r="D16" s="0">
+        <v>0</v>
+      </c>
+      <c r="E16" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" s="0">
+        <v>1892898805</v>
+      </c>
+      <c r="C17" s="0">
+        <v>0</v>
+      </c>
+      <c r="D17" s="0">
+        <v>0</v>
+      </c>
+      <c r="E17" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" s="0">
+        <v>2337278790</v>
+      </c>
+      <c r="C18" s="0">
+        <v>0</v>
+      </c>
+      <c r="D18" s="0">
+        <v>0</v>
+      </c>
+      <c r="E18" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19" s="0">
+        <v>1891756440</v>
+      </c>
+      <c r="C19" s="0">
+        <v>0</v>
+      </c>
+      <c r="D19" s="0">
+        <v>0</v>
+      </c>
+      <c r="E19" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" s="0">
+        <v>1171672145</v>
+      </c>
+      <c r="C20" s="0">
+        <v>0</v>
+      </c>
+      <c r="D20" s="0">
+        <v>0</v>
+      </c>
+      <c r="E20" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21" s="0">
+        <v>1331642596</v>
+      </c>
+      <c r="C21" s="0">
+        <v>0</v>
+      </c>
+      <c r="D21" s="0">
+        <v>0</v>
+      </c>
+      <c r="E21" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22" s="0">
+        <v>2239565824</v>
+      </c>
+      <c r="C22" s="0">
+        <v>0</v>
+      </c>
+      <c r="D22" s="0">
+        <v>0</v>
+      </c>
+      <c r="E22" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" s="0">
+        <v>2126931410</v>
+      </c>
+      <c r="C23" s="0">
+        <v>0</v>
+      </c>
+      <c r="D23" s="0">
+        <v>0</v>
+      </c>
+      <c r="E23" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="B24" s="0">
+        <v>2105709546</v>
+      </c>
+      <c r="C24" s="0">
+        <v>0</v>
+      </c>
+      <c r="D24" s="0">
+        <v>0</v>
+      </c>
+      <c r="E24" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="B25" s="0">
+        <v>2902133356</v>
+      </c>
+      <c r="C25" s="0">
+        <v>0</v>
+      </c>
+      <c r="D25" s="0">
+        <v>0</v>
+      </c>
+      <c r="E25" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" s="0">
+        <v>3406243372</v>
+      </c>
+      <c r="C26" s="0">
+        <v>0</v>
+      </c>
+      <c r="D26" s="0">
+        <v>0</v>
+      </c>
+      <c r="E26" s="0">
         <v>0</v>
       </c>
     </row>
